--- a/consent_forms/031_foster_care_agreement_form--consent_forms.xlsx
+++ b/consent_forms/031_foster_care_agreement_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>foster_care_agreement</t>
+          <t>Is the child in your care a child of yours?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_of_child</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>foster_parent_name</t>
+          <t>Name of Child</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,110 +566,110 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name_of_child</t>
+          <t>birth_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>name_of_child</t>
+          <t>Birth Details (including birthdate)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>birthdate_of_child</t>
+          <t>contact_details</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>birthdate_of_child</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>birthdate_of_child</t>
+          <t>agency_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>birthdate_of_child</t>
+          <t>Agency Name and Address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>agreement_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>Date of Agreement</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>care_duration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Dates of Care (start and end)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,154 +681,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>agency_name</t>
+          <t>caregiver_details</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>agency_name</t>
+          <t>Your Contact Information</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>agency_address</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>agency_address</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>date_of_agreement</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>date_of_agreement</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>date_of_agreement</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>date_of_agreement</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,6 +786,57 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>care_duration_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>care_duration_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>care_duration_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
